--- a/XlsxSharp.Tests/Resource/Other/Styles/Alignment/TextRotation.xlsx
+++ b/XlsxSharp.Tests/Resource/Other/Styles/Alignment/TextRotation.xlsx
@@ -1,81 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Sheet1" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Vertical: 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: -10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rotation: 90</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Vertical: 255</t>
+  </si>
+  <si>
+    <t>Rotation: -90</t>
+  </si>
+  <si>
+    <t>Rotation: -80</t>
+  </si>
+  <si>
+    <t>Rotation: -70</t>
+  </si>
+  <si>
+    <t>Rotation: -60</t>
+  </si>
+  <si>
+    <t>Rotation: -50</t>
+  </si>
+  <si>
+    <t>Rotation: -40</t>
+  </si>
+  <si>
+    <t>Rotation: -30</t>
+  </si>
+  <si>
+    <t>Rotation: -20</t>
+  </si>
+  <si>
+    <t>Rotation: -10</t>
+  </si>
+  <si>
+    <t>Rotation: 0</t>
+  </si>
+  <si>
+    <t>Rotation: 10</t>
+  </si>
+  <si>
+    <t>Rotation: 20</t>
+  </si>
+  <si>
+    <t>Rotation: 30</t>
+  </si>
+  <si>
+    <t>Rotation: 40</t>
+  </si>
+  <si>
+    <t>Rotation: 50</t>
+  </si>
+  <si>
+    <t>Rotation: 60</t>
+  </si>
+  <si>
+    <t>Rotation: 70</t>
+  </si>
+  <si>
+    <t>Rotation: 80</t>
+  </si>
+  <si>
+    <t>Rotation: 90</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -469,80 +469,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:T1"/>
-  <x:sheetFormatPr defaultColWidth="10.710625" defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:20">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="7" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I1" s="9" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K1" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L1" s="12" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M1" s="13" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N1" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="O1" s="15" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="P1" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="Q1" s="17" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="R1" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="S1" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="T1" s="20" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="10.710625"/>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>